--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_936_Guatemala_Pacific.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_936_Guatemala_Pacific.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rd6be529229994289"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R5628c4c5555c497d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rf0bbbad1659b4aed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R668479f5f70f4f0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R1b6f97959d12412c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R76ca8a5dc64a4100"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Re1eb542461b34ce3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rb51f94119d304974"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R03bd8c3c78284554"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rdf6d1a34862d4f9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rfe32736701d24193"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R384f8d5db18e41b9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ936CommercialTable" displayName="EEZ936CommercialTable" ref="A1:O10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O10"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ936CommercialTable" displayName="EEZ936CommercialTable" ref="A1:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E10"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ936FunctionalTable" displayName="EEZ936FunctionalTable" ref="A1:O19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O19"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ936FunctionalTable" displayName="EEZ936FunctionalTable" ref="A1:E19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E19"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ936ValidationTable" displayName="EEZ936ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ936ValidationTable" displayName="EEZ936ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -5853,7 +5807,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ea7378392764e51"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reefa7184f0ec418e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5863,20 +5817,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5884,552 +5828,193 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>2241.345438623</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.0273947735976576</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>106.51107637898238</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>2241.345438623</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>146.71123562074087</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$78,A2,'Species'!$U$2:$U$78))</x:f>
-        <x:v>328830.5587532917</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.0273947735976576</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>106.51107637898238</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>238728.11520485813</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>90102.4435484336</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.3774270302059504</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.3774270302059504</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>2474.4189983750002</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.053817332349938</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1131.9241669539506</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>2474.4189983750002</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1140.2915832048293</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$78,A3,'Species'!$U$2:$U$78))</x:f>
-        <x:v>2821559.157169137</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.053817332349938</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1131.9241669539506</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>2800854.6634306507</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>20704.49373848643</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.007392205675223</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.007392205675222846</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.19778770810000001</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.89</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>77.6247116628692</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.19778770810000001</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>77.6247116628692</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$78,A4,'Species'!$U$2:$U$78))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>15.35321381172224</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.89</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>77.6247116628692</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>15.35321381172224</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>216.921012352</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.0001622146689177</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>10.003735828432106</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>216.921012352</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>10.00420014999486</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$78,A5,'Species'!$U$2:$U$78))</x:f>
-        <x:v>2170.1212243089153</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.0001622146689177</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>10.003735828432106</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>2170.0205032054655</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0.10072110344981411</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0000464148164965</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.000046414816496449234</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>6532.774759254799</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.372974208575398</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>236.03380557405987</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>6532.774759254799</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>326.74744615268116</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$78,A6,'Species'!$U$2:$U$78))</x:f>
-        <x:v>2134567.4688772024</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.372974208575398</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>236.03380557405987</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1541955.6873850732</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>592611.7814921292</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.3843247807575523</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.3843247807575524</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>18731.040679590602</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.7628977758793543</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>579.2923267030508</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>18731.040679590602</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>788.3212947419325</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$78,A7,'Species'!$U$2:$U$78))</x:f>
-        <x:v>14766078.240398671</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.7628977758793543</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>579.2923267030508</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>10850748.136849534</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>3915330.1035491377</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.3608350368259434</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.36083503682594337</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>97.06522535</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.763893805315314</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>580.6224250322658</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>97.06522535</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>587.0040903148306</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$78,A8,'Species'!$U$2:$U$78))</x:f>
-        <x:v>56977.684307780786</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.763893805315314</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>580.6224250322658</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>56358.24652902037</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>619.4377787604171</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0109910761407641</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.010991076140764104</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>830.1366039041</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.961166764257829</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>914.4643182034134</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>830.1366039041</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1590.4303689522228</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$78,A9,'Species'!$U$2:$U$78))</x:f>
-        <x:v>1320274.465227943</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.961166764257829</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>914.4643182034134</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>759130.3035048598</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>561144.1617230831</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.739193468015061</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.739193468015061</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>1022.9251987472002</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.380803183402425</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2403.2734209949613</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>1022.9251987472002</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2497.195625122351</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$78,A10,'Species'!$U$2:$U$78))</x:f>
-        <x:v>2554444.3311389196</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.380803183402425</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2403.2734209949613</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2458368.9418151346</x:v>
       </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>96075.38932378497</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0390809482212413</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.03908094822124127</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G10">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O10">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R584ec0d5385e45f6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ac7f45766ed44fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6439,20 +6024,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6460,1038 +6035,364 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>224.65697554599998</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.139639991552618</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1379.240469090574</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>224.65697554599998</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1379.2530683076357</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$78,A2,'Species'!$U$2:$U$78))</x:f>
-        <x:v>309858.82283853396</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.139639991552618</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1379.240469090574</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>309855.9923365346</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>2.830501999356784</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0000091348951428</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.000009134895142781604</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>265.172820028</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.4712019253961484</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>295.9388115431453</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>265.172820028</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1457.9538572854701</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$78,A3,'Species'!$U$2:$U$78))</x:f>
-        <x:v>386609.7358070884</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.4712019253961484</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>295.9388115431453</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>78474.92921263067</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>308134.8065944577</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>4.926538191064248</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>3.926538191064248</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>54.616317728</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.35</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2238.7211385683377</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>54.616317728</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$78,A4,'Species'!$U$2:$U$78))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>122270.70500843824</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.35</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>122270.70500843824</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1572.1145477890998</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.399527596242459</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2509.155612913535</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1572.1145477890998</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2521.6498063788235</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$78,A5,'Species'!$U$2:$U$78))</x:f>
-        <x:v>3964322.3450377155</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.399527596242459</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2509.155612913535</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>3944680.041728044</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>19642.30330967158</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.004979441450736</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.004979441450735986</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>388.754846019</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.4699026199639493</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>295.05475635431674</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>388.754846019</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>320.1218190854634</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$78,A6,'Species'!$U$2:$U$78))</x:f>
-        <x:v>124448.90848589152</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.4699026199639493</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>295.05475635431674</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>114703.96637369596</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>9744.942112195553</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0849573246704245</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.08495732467042459</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>393.662757817</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.7531404862922155</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>566.4224866823039</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>393.662757817</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>609.1888606868326</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$78,A7,'Species'!$U$2:$U$78))</x:f>
-        <x:v>239814.96692937473</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.7531404862922155</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>566.4224866823039</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>222979.4381969187</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>16835.528732456034</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0755026062877966</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.07550260628779663</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>441.38175788510006</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.393856410709731</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2476.603091495905</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>441.38175788510006</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2709.2772534866453</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$78,A8,'Species'!$U$2:$U$78))</x:f>
-        <x:v>1195825.5567420514</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.393856410709731</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2476.603091495905</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1093127.4261081358</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>102698.13063391554</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0939489104207658</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.09394891042076581</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>862.293504658</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>2.9436862881886845</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>87.83877858266099</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>862.293504658</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>99.17817300707952</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$78,A9,'Species'!$U$2:$U$78))</x:f>
-        <x:v>85520.69438785205</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>2.9436862881886845</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>87.83877858266099</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>75742.80822892081</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>9777.886158931244</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1290932616253033</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.1290932616253032</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>324.853701944</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.1366666666181113</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>136.98299790618194</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>324.853701944</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>337.5357990450119</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$78,A10,'Species'!$U$2:$U$78))</x:f>
-        <x:v>109649.7538583982</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.1366666666181113</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>136.98299790618194</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>44499.433973210405</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>65150.31988518779</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>2.4640707547967837</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>1.4640707547967835</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>15896.351295142902</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.469506555822803</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>294.7857975188648</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>15896.351295142902</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>396.0201449807339</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$78,A11,'Species'!$U$2:$U$78))</x:f>
-        <x:v>6295275.344567169</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.469506555822803</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>294.7857975188648</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>4686018.59417874</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>1609256.7503884295</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.3434166378228944</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.3434166378228945</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>65.8715860486</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.838769327925956</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>689.8732857809761</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>65.8715860486</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>704.8146838702232</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$78,A12,'Species'!$U$2:$U$78))</x:f>
-        <x:v>46427.26109687421</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.838769327925956</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>689.8732857809761</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>45443.04750695198</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>984.2135899222267</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0216581775192708</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.021658177519270894</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>7438.621304226</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.028336374402993</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1067.422552662654</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>7438.621304226</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1075.270862057009</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$78,A13,'Species'!$U$2:$U$78))</x:f>
-        <x:v>7998532.742310723</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.028336374402993</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1067.422552662654</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>7940152.1408477165</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>58380.60146300681</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0073525797021785</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.007352579702178592</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>216.921012352</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.0001622146689177</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>10.003735828432106</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>216.921012352</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>10.00420014999486</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$78,A14,'Species'!$U$2:$U$78))</x:f>
-        <x:v>2170.1212243089153</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.0001622146689177</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>10.003735828432106</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>2170.0205032054655</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>0.10072110344981411</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0000464148164965</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.000046414816496449234</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>1379.0519339650002</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.079736009975451</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>120.15338488343073</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>1379.0519339650002</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>176.43270595755155</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$78,A15,'Species'!$U$2:$U$78))</x:f>
-        <x:v>243309.86436543966</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.079736009975451</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>120.15338488343073</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>165697.75779593617</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>77612.10656950349</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.4683956355347072</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.46839563553470714</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>72.138319892</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.03</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>107.1519305237606</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>72.138319892</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>107.1519305237606</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$78,A16,'Species'!$U$2:$U$78))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>7729.760241168401</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.03</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>107.1519305237606</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>7729.760241168401</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>75.746236781</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.6200000000000006</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>416.86938347033595</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>75.746236781</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>416.8693834703355</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$78,A17,'Species'!$U$2:$U$78))</x:f>
-        <x:v>31576.287027093516</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.6200000000000006</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>416.86938347033595</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>31576.287027093553</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>-3.637978807091713e-11</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>0.9999999999999989</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>-1.1521236819168133e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>0.19778770810000001</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.89</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>77.6247116628692</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>0.19778770810000001</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>77.6247116628692</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$78,A18,'Species'!$U$2:$U$78))</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>15.35321381172224</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.89</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>77.6247116628692</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
-        <x:v>15.35321381172224</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>2474.4189983750002</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>4.053817332349938</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>1131.9241669539506</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>2474.4189983750002</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>1140.2915832048293</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$78,A19,'Species'!$U$2:$U$78))</x:f>
-        <x:v>2821559.157169137</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>4.053817332349938</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>1131.9241669539506</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>2800854.6634306507</x:v>
       </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>20704.49373848643</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.007392205675223</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.007392205675222846</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G19">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O19">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5c9f8ad85104fa3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2361589710e242e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7666,7 +6567,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -7765,7 +6666,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>23984917.380311072</x:v>
+        <x:v>18708329.468436148</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7779,7 +6680,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>23984917.38031107</x:v>
+        <x:v>21685992.365911804</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7793,7 +6694,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-5276587.911874924</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7807,7 +6708,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-3.725290298461914e-9</x:v>
+        <x:v>-2298925.0143992677</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7818,9 +6719,9 @@
         <x:v>EEZ_936</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -7832,47 +6733,19 @@
         <x:v>EEZ_936</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_936</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_936</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fa4daebbe4945fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33dfd14c3371435c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7919,7 +6792,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
